--- a/data/raw/market/Bloomberg_MarketData_20261006.xlsx
+++ b/data/raw/market/Bloomberg_MarketData_20261006.xlsx
@@ -2,10 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USD" sheetId="1" r:id="R746830598a4f42f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EUR" sheetId="2" r:id="Rb66223e8d40d49d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GBP" sheetId="3" r:id="R8756d1be8e394f0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AUD" sheetId="4" r:id="R475ac641bcf8406a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USD" sheetId="1" r:id="R0340e568aa7a452d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EUR" sheetId="2" r:id="R6273b73c62454c73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GBP" sheetId="3" r:id="Rf6d076aa73814350"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AUD" sheetId="4" r:id="R9f8981dc416a477b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPY" sheetId="5" r:id="Rebb06d21e5a143e3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,9 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="200" formatCode="yyyy/m/d"/>
     <x:numFmt numFmtId="201" formatCode="0.000"/>
+    <x:numFmt numFmtId="202" formatCode="0.00000000"/>
   </x:numFmts>
   <x:fonts count="4">
     <x:font>
@@ -72,7 +74,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -81,6 +83,7 @@
     <x:xf numFmtId="200" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -2883,4 +2886,284 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="33" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="110" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>marketdate</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>tenor</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>ticker</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>Ask Yield</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str">
+        <x:v>Mid Yield</x:v>
+      </x:c>
+      <x:c r="F1" s="3" t="str">
+        <x:v>Bid Yield</x:v>
+      </x:c>
+      <x:c r="H1" s="7" t="str">
+        <x:v>Source: existing TONAR quotes in R/set_market_data_for_assetswap.R (commit 369f283).</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="5" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="B2" s="4" t="str">
+        <x:v>1M</x:v>
+      </x:c>
+      <x:c r="C2" s="4" t="str">
+        <x:v>TONAR_OIS_1M</x:v>
+      </x:c>
+      <x:c r="D2" s="8"/>
+      <x:c r="E2" s="8" t="n">
+        <x:v>1.23</x:v>
+      </x:c>
+      <x:c r="F2" s="8"/>
+      <x:c r="H2" s="7" t="str">
+        <x:v>2026-10-06 only. These JPY observations were not supplied as Bloomberg quotes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="5" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="str">
+        <x:v>3M</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="str">
+        <x:v>TONAR_OIS_3M</x:v>
+      </x:c>
+      <x:c r="D3" s="8"/>
+      <x:c r="E3" s="8" t="n">
+        <x:v>1.29</x:v>
+      </x:c>
+      <x:c r="F3" s="8"/>
+      <x:c r="H3" s="7" t="str">
+        <x:v>Mid yields in percent. Ask/Bid are unavailable and remain blank.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="5" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="str">
+        <x:v>6M</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="str">
+        <x:v>TONAR_OIS_6M</x:v>
+      </x:c>
+      <x:c r="D4" s="8"/>
+      <x:c r="E4" s="8" t="n">
+        <x:v>1.42</x:v>
+      </x:c>
+      <x:c r="F4" s="8"/>
+      <x:c r="H4" s="7" t="str">
+        <x:v>TONAR_OIS_* are internal identifiers, not Bloomberg tickers.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="5" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="B5" s="4" t="str">
+        <x:v>1Y</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="str">
+        <x:v>TONAR_OIS_1Y</x:v>
+      </x:c>
+      <x:c r="D5" s="8"/>
+      <x:c r="E5" s="8" t="n">
+        <x:v>1.65</x:v>
+      </x:c>
+      <x:c r="F5" s="8"/>
+      <x:c r="H5" s="7" t="str">
+        <x:v>Original tenor dates were not supplied; the curve builder calculates tenordate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="5" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="str">
+        <x:v>2Y</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="str">
+        <x:v>TONAR_OIS_2Y</x:v>
+      </x:c>
+      <x:c r="D6" s="8"/>
+      <x:c r="E6" s="8" t="n">
+        <x:v>1.93</x:v>
+      </x:c>
+      <x:c r="F6" s="8"/>
+      <x:c r="H6" s="7" t="str">
+        <x:v>The 2022 historical example remains in the R scripts.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="5" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="str">
+        <x:v>3Y</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="str">
+        <x:v>TONAR_OIS_3Y</x:v>
+      </x:c>
+      <x:c r="D7" s="8"/>
+      <x:c r="E7" s="8" t="n">
+        <x:v>2.11</x:v>
+      </x:c>
+      <x:c r="F7" s="8"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="5" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="B8" s="4" t="str">
+        <x:v>4Y</x:v>
+      </x:c>
+      <x:c r="C8" s="4" t="str">
+        <x:v>TONAR_OIS_4Y</x:v>
+      </x:c>
+      <x:c r="D8" s="8"/>
+      <x:c r="E8" s="8" t="n">
+        <x:v>2.26</x:v>
+      </x:c>
+      <x:c r="F8" s="8"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="5" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="str">
+        <x:v>5Y</x:v>
+      </x:c>
+      <x:c r="C9" s="4" t="str">
+        <x:v>TONAR_OIS_5Y</x:v>
+      </x:c>
+      <x:c r="D9" s="8"/>
+      <x:c r="E9" s="8" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="F9" s="8"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="5" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="B10" s="4" t="str">
+        <x:v>7Y</x:v>
+      </x:c>
+      <x:c r="C10" s="4" t="str">
+        <x:v>TONAR_OIS_7Y</x:v>
+      </x:c>
+      <x:c r="D10" s="8"/>
+      <x:c r="E10" s="8" t="n">
+        <x:v>2.65197582</x:v>
+      </x:c>
+      <x:c r="F10" s="8"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="5" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="B11" s="4" t="str">
+        <x:v>8Y</x:v>
+      </x:c>
+      <x:c r="C11" s="4" t="str">
+        <x:v>TONAR_OIS_8Y</x:v>
+      </x:c>
+      <x:c r="D11" s="8"/>
+      <x:c r="E11" s="8" t="n">
+        <x:v>2.76376531</x:v>
+      </x:c>
+      <x:c r="F11" s="8"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="5" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="B12" s="4" t="str">
+        <x:v>10Y</x:v>
+      </x:c>
+      <x:c r="C12" s="4" t="str">
+        <x:v>TONAR_OIS_10Y</x:v>
+      </x:c>
+      <x:c r="D12" s="8"/>
+      <x:c r="E12" s="8" t="n">
+        <x:v>2.96</x:v>
+      </x:c>
+      <x:c r="F12" s="8"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="5" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="B13" s="4" t="str">
+        <x:v>15Y</x:v>
+      </x:c>
+      <x:c r="C13" s="4" t="str">
+        <x:v>TONAR_OIS_15Y</x:v>
+      </x:c>
+      <x:c r="D13" s="8"/>
+      <x:c r="E13" s="8" t="n">
+        <x:v>3.31477453</x:v>
+      </x:c>
+      <x:c r="F13" s="8"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="5" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="B14" s="4" t="str">
+        <x:v>20Y</x:v>
+      </x:c>
+      <x:c r="C14" s="4" t="str">
+        <x:v>TONAR_OIS_20Y</x:v>
+      </x:c>
+      <x:c r="D14" s="8"/>
+      <x:c r="E14" s="8" t="n">
+        <x:v>3.56</x:v>
+      </x:c>
+      <x:c r="F14" s="8"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="5" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="B15" s="4" t="str">
+        <x:v>30Y</x:v>
+      </x:c>
+      <x:c r="C15" s="4" t="str">
+        <x:v>TONAR_OIS_30Y</x:v>
+      </x:c>
+      <x:c r="D15" s="8"/>
+      <x:c r="E15" s="8" t="n">
+        <x:v>4.01393458</x:v>
+      </x:c>
+      <x:c r="F15" s="8"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>